--- a/222/222_222/011_BKU1/条件输入数据表.xlsx
+++ b/222/222_222/011_BKU1/条件输入数据表.xlsx
@@ -1946,8 +1946,16 @@
           <t>MPa</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="25" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
           <t>工作温度（出口）</t>
@@ -2058,8 +2066,16 @@
           <t>℃</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="25" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="41" t="inlineStr">
@@ -2134,8 +2150,16 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="25" t="inlineStr"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="41" t="inlineStr">
